--- a/API Test Cases.xlsx
+++ b/API Test Cases.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\API Testing Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\API Testing Projects\ReqRes API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBDD7A5-22C0-4E14-B2A9-3CBFB29F2794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77ED3DC-9242-446C-96CA-80F0762FBC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="0" windowWidth="12000" windowHeight="13500" xr2:uid="{DBF2489D-0C4C-4E23-9F36-6BF3AC1EAEA3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1" xr2:uid="{DBF2489D-0C4C-4E23-9F36-6BF3AC1EAEA3}"/>
   </bookViews>
   <sheets>
-    <sheet name="REQRES API" sheetId="1" r:id="rId1"/>
+    <sheet name="REQRES API Test Case" sheetId="1" r:id="rId1"/>
+    <sheet name="Student API Test Case" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
   <si>
     <t>TCID</t>
   </si>
@@ -100,12 +101,144 @@
   <si>
     <t>https://reqres.in/api/users/540</t>
   </si>
+  <si>
+    <t>Title/Descrription</t>
+  </si>
+  <si>
+    <t>HTTP Request</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Validations</t>
+  </si>
+  <si>
+    <t>Get Single Student Data</t>
+  </si>
+  <si>
+    <t>Get All Students Data</t>
+  </si>
+  <si>
+    <t>Create New Student</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/students/1</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/students</t>
+  </si>
+  <si>
+    <t>{
+      "id": "1",
+      "name": "John",
+      "location": "India",
+      "phone": "1234567890",
+      "course": [
+        "Java",
+        "Selenium"
+      ]
+    }</t>
+  </si>
+  <si>
+    <t>{
+      "name": "Eden",
+      "location": "Paris",
+      "phone": "1234567890",
+      "course": [
+        "Postman",
+        "Selenium"
+      ]
+    }</t>
+  </si>
+  <si>
+    <t>{
+      "id": "1",
+      "name": "John",
+      "location": "India",
+      "phone": "1234567890",
+      "course": [
+        "Java",
+        "Selenium"
+      ]
+    },
+    {
+      "id": "2",
+      "name": "Kim",
+      "location": "US",
+      "phone": "98876543213",
+      "course": [
+        "Python",
+        "Appium"
+      ]
+    },
+    {
+      "id": "3",
+      "name": "Smith",
+      "location": "Canada",
+      "phone": "165498765",
+      "course": [
+        "C#",
+        "RestAPI"
+      ]
+    },
+    {
+      "name": "Eden",
+      "location": "France",
+      "phone": "7010381670",
+      "course": [
+        "R",
+        "Java"
+      ],
+      "id": "7864"
+    },
+    {
+      "id": "5c39",
+      "name": "Eden",
+      "location": "Nigeria",
+      "phone": "7010381670",
+      "course": [
+        "R",
+        "Java"
+      ]
+    },
+    {
+      "id": "91fe",
+      "name": "Jackson",
+      "location": "France",
+      "phone": "234556",
+      "courses": [
+        "C#",
+        "Python"
+      ]
+    }</t>
+  </si>
+  <si>
+    <t>Update Student</t>
+  </si>
+  <si>
+    <t>Delete Student</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/students/4</t>
+  </si>
+  <si>
+    <t>{
+      "name": "Eden",
+      "location": "Paris",
+      "phone": "456557373",
+      "course": [
+        "Postman",
+        "Automation"
+      ]
+    }</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,13 +260,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -164,7 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -178,6 +325,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -616,4 +772,190 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7039763-FE7B-41F3-9EA1-B5BACF96E540}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.85546875" customWidth="1"/>
+    <col min="7" max="7" width="35.28515625" customWidth="1"/>
+    <col min="8" max="8" width="23" style="7" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="171" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="4">
+        <v>200</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="4">
+        <v>200</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="4">
+        <v>201</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="4">
+        <v>200</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="4">
+        <v>200</v>
+      </c>
+      <c r="I6" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{7BF0B4C0-7E1D-455B-89C5-DCCB7014194F}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{DBA0C255-5FA1-4633-8238-5835AE201452}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{82E2C277-FB37-413A-8A22-5A4285D9F81F}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{49C56580-1B17-4650-A8AB-2F87459F5EAC}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{0718EEE0-3B8B-4C18-A3C4-D5B3762477B3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/API Test Cases.xlsx
+++ b/API Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\API Testing Projects\ReqRes API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77ED3DC-9242-446C-96CA-80F0762FBC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35447A2E-2EBD-41AA-BB0E-3C6F6CAD2722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1" xr2:uid="{DBF2489D-0C4C-4E23-9F36-6BF3AC1EAEA3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>TCID</t>
   </si>
@@ -129,16 +129,89 @@
     <t>http://localhost:3000/students</t>
   </si>
   <si>
+    <t>Update Student</t>
+  </si>
+  <si>
+    <t>Delete Student</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/students/4</t>
+  </si>
+  <si>
     <t>{
-      "id": "1",
-      "name": "John",
-      "location": "India",
-      "phone": "1234567890",
-      "course": [
+    "id": "1",
+    "name": "John",
+    "location": "India",
+    "phone": "1234567890",
+    "course": [
         "Java",
         "Selenium"
-      ]
-    }</t>
+    ]
+}</t>
+  </si>
+  <si>
+    <t>[
+    {
+        "id": "1",
+        "name": "John",
+        "location": "India",
+        "phone": "1234567890",
+        "course": [
+            "Java",
+            "Selenium"
+        ]
+    },
+    {
+        "id": "2",
+        "name": "Kim",
+        "location": "US",
+        "phone": "98876543213",
+        "course": [
+            "Python",
+            "Appium"
+        ]
+    },
+    {
+        "id": "3",
+        "name": "Smith",
+        "location": "Canada",
+        "phone": "165498765",
+        "course": [
+            "C#",
+            "RestAPI"
+        ]
+    },
+    {
+        "name": "Eden",
+        "location": "France",
+        "phone": "7010381670",
+        "course": [
+            "R",
+            "Java"
+        ],
+        "id": "7864"
+    },
+    {
+        "id": "5c39",
+        "name": "Eden",
+        "location": "Nigeria",
+        "phone": "7010381670",
+        "course": [
+            "R",
+            "Java"
+        ]
+    },
+    {
+        "id": "91fe",
+        "name": "Jackson",
+        "location": "France",
+        "phone": "234556",
+        "courses": [
+            "C#",
+            "Python"
+        ]
+    }
+]</t>
   </si>
   <si>
     <t>{
@@ -149,78 +222,19 @@
         "Postman",
         "Selenium"
       ]
-    }</t>
+}</t>
   </si>
   <si>
     <t>{
-      "id": "1",
-      "name": "John",
-      "location": "India",
-      "phone": "1234567890",
-      "course": [
-        "Java",
+    "id": "38b3",
+    "name": "Eden",
+    "location": "Paris",
+    "phone": "1234567890",
+    "course": [
+        "Postman",
         "Selenium"
-      ]
-    },
-    {
-      "id": "2",
-      "name": "Kim",
-      "location": "US",
-      "phone": "98876543213",
-      "course": [
-        "Python",
-        "Appium"
-      ]
-    },
-    {
-      "id": "3",
-      "name": "Smith",
-      "location": "Canada",
-      "phone": "165498765",
-      "course": [
-        "C#",
-        "RestAPI"
-      ]
-    },
-    {
-      "name": "Eden",
-      "location": "France",
-      "phone": "7010381670",
-      "course": [
-        "R",
-        "Java"
-      ],
-      "id": "7864"
-    },
-    {
-      "id": "5c39",
-      "name": "Eden",
-      "location": "Nigeria",
-      "phone": "7010381670",
-      "course": [
-        "R",
-        "Java"
-      ]
-    },
-    {
-      "id": "91fe",
-      "name": "Jackson",
-      "location": "France",
-      "phone": "234556",
-      "courses": [
-        "C#",
-        "Python"
-      ]
-    }</t>
-  </si>
-  <si>
-    <t>Update Student</t>
-  </si>
-  <si>
-    <t>Delete Student</t>
-  </si>
-  <si>
-    <t>http://localhost:3000/students/4</t>
+    ]
+}</t>
   </si>
   <si>
     <t>{
@@ -231,7 +245,22 @@
         "Postman",
         "Automation"
       ]
-    }</t>
+}</t>
+  </si>
+  <si>
+    <t>{
+    "name": "Eden",
+    "location": "Paris",
+    "phone": "456557373",
+    "course": [
+        "Postman",
+        "Automation"
+    ],
+    "id": 4
+}</t>
+  </si>
+  <si>
+    <t>{}</t>
   </si>
 </sst>
 </file>
@@ -311,7 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -334,6 +363,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -782,7 +814,7 @@
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.85546875" customWidth="1"/>
     <col min="7" max="7" width="35.28515625" customWidth="1"/>
@@ -829,7 +861,7 @@
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -839,7 +871,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H2" s="4">
         <v>200</v>
@@ -856,7 +888,7 @@
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -866,14 +898,14 @@
         <v>12</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4">
         <v>200</v>
       </c>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -883,41 +915,45 @@
       <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="H4" s="4">
         <v>201</v>
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="H5" s="4">
         <v>200</v>
       </c>
@@ -928,12 +964,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -942,7 +978,9 @@
       <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="H6" s="4">
         <v>200</v>
       </c>
